--- a/master/result/56_穿越修仙_青云之路/56_穿越修仙_青云之路.xlsx
+++ b/master/result/56_穿越修仙_青云之路/56_穿越修仙_青云之路.xlsx
@@ -397,511 +397,647 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C45"/>
+  <dimension ref="A1:D45"/>
   <cols>
-    <col min="1" max="1" width="8.83203125" customWidth="1"/>
+    <col min="1" max="1" width="15.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
-    <col min="3" max="3" width="30.83203125" customWidth="1"/>
+    <col min="3" max="3" width="8.83203125" customWidth="1"/>
+    <col min="4" max="4" width="15.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>序号</v>
+        <v>词汇</v>
       </c>
       <c r="B1" t="str">
-        <v>单词</v>
+        <v>音标</v>
       </c>
       <c r="C1" t="str">
-        <v>中文含义</v>
+        <v>词性</v>
+      </c>
+      <c r="D1" t="str">
+        <v>中文</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2">
-        <v>1</v>
+      <c r="A2" t="str">
+        <v>morning</v>
       </c>
       <c r="B2" t="str">
-        <v>morning</v>
+        <v>/morning/</v>
       </c>
       <c r="C2" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D2" t="str">
         <v>早晨</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3">
-        <v>2</v>
+      <c r="A3" t="str">
+        <v>slope</v>
       </c>
       <c r="B3" t="str">
-        <v>slope</v>
+        <v>/slope/</v>
       </c>
       <c r="C3" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D3" t="str">
         <v>斜坡</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4">
-        <v>3</v>
+      <c r="A4" t="str">
+        <v>fiction</v>
       </c>
       <c r="B4" t="str">
-        <v>fiction</v>
+        <v>/fiction/</v>
       </c>
       <c r="C4" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D4" t="str">
         <v>小说</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5">
-        <v>4</v>
+      <c r="A5" t="str">
+        <v>form</v>
       </c>
       <c r="B5" t="str">
-        <v>form</v>
+        <v>/fɔːm/</v>
       </c>
       <c r="C5" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D5" t="str">
         <v>形式</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6">
-        <v>5</v>
+      <c r="A6" t="str">
+        <v>difficulty</v>
       </c>
       <c r="B6" t="str">
-        <v>difficulty</v>
+        <v>/difficulty/</v>
       </c>
       <c r="C6" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D6" t="str">
         <v>困难</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7">
-        <v>6</v>
+      <c r="A7" t="str">
+        <v>shed</v>
       </c>
       <c r="B7" t="str">
-        <v>shed</v>
+        <v>/shed/</v>
       </c>
       <c r="C7" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D7" t="str">
         <v>棚</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8">
-        <v>7</v>
+      <c r="A8" t="str">
+        <v>artist</v>
       </c>
       <c r="B8" t="str">
-        <v>artist</v>
+        <v>/ˈɑːtɪst/</v>
       </c>
       <c r="C8" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D8" t="str">
         <v>艺术家</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9">
-        <v>8</v>
+      <c r="A9" t="str">
+        <v>anecdote</v>
       </c>
       <c r="B9" t="str">
-        <v>anecdote</v>
+        <v>/anecdote/</v>
       </c>
       <c r="C9" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D9" t="str">
         <v>轶事</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10">
-        <v>9</v>
+      <c r="A10" t="str">
+        <v>volcano</v>
       </c>
       <c r="B10" t="str">
-        <v>volcano</v>
+        <v>/volcano/</v>
       </c>
       <c r="C10" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D10" t="str">
         <v>火山</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11">
-        <v>10</v>
+      <c r="A11" t="str">
+        <v>constant</v>
       </c>
       <c r="B11" t="str">
-        <v>constant</v>
+        <v>/ˈkɒnstənt/</v>
       </c>
       <c r="C11" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D11" t="str">
         <v>不断的</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12">
-        <v>11</v>
+      <c r="A12" t="str">
+        <v>committee</v>
       </c>
       <c r="B12" t="str">
-        <v>committee</v>
+        <v>/committee/</v>
       </c>
       <c r="C12" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D12" t="str">
         <v>委员会</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13">
-        <v>12</v>
+      <c r="A13" t="str">
+        <v>guide</v>
       </c>
       <c r="B13" t="str">
-        <v>guide</v>
+        <v>/ɡaɪd/</v>
       </c>
       <c r="C13" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D13" t="str">
         <v>指导者</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14">
-        <v>13</v>
+      <c r="A14" t="str">
+        <v>cousin</v>
       </c>
       <c r="B14" t="str">
-        <v>cousin</v>
+        <v>/ˈkʌzən/</v>
       </c>
       <c r="C14" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D14" t="str">
         <v>表亲</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15">
-        <v>14</v>
+      <c r="A15" t="str">
+        <v>inn</v>
       </c>
       <c r="B15" t="str">
-        <v>inn</v>
+        <v>/inn/</v>
       </c>
       <c r="C15" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D15" t="str">
         <v>客栈</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16">
-        <v>15</v>
+      <c r="A16" t="str">
+        <v>noise</v>
       </c>
       <c r="B16" t="str">
-        <v>noise</v>
+        <v>/noise/</v>
       </c>
       <c r="C16" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D16" t="str">
         <v>噪音</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17">
-        <v>16</v>
+      <c r="A17" t="str">
+        <v>worry</v>
       </c>
       <c r="B17" t="str">
-        <v>worry</v>
+        <v>/ˈwʌri/</v>
       </c>
       <c r="C17" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D17" t="str">
         <v>担心</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18">
-        <v>17</v>
+      <c r="A18" t="str">
+        <v>stride</v>
       </c>
       <c r="B18" t="str">
-        <v>stride</v>
+        <v>/stride/</v>
       </c>
       <c r="C18" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D18" t="str">
         <v>大步走</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19">
-        <v>18</v>
+      <c r="A19" t="str">
+        <v>sound</v>
       </c>
       <c r="B19" t="str">
-        <v>sound</v>
+        <v>/saʊnd/</v>
       </c>
       <c r="C19" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D19" t="str">
         <v>声音</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20">
-        <v>19</v>
+      <c r="A20" t="str">
+        <v>spring</v>
       </c>
       <c r="B20" t="str">
-        <v>spring</v>
+        <v>/sprɪŋ/</v>
       </c>
       <c r="C20" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D20" t="str">
         <v>春天</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21">
-        <v>20</v>
+      <c r="A21" t="str">
+        <v>array</v>
       </c>
       <c r="B21" t="str">
-        <v>array</v>
+        <v>/array/</v>
       </c>
       <c r="C21" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D21" t="str">
         <v>排列</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22">
-        <v>21</v>
+      <c r="A22" t="str">
+        <v>warmth</v>
       </c>
       <c r="B22" t="str">
-        <v>warmth</v>
+        <v>/warmth/</v>
       </c>
       <c r="C22" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D22" t="str">
         <v>温暖</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23">
-        <v>22</v>
+      <c r="A23" t="str">
+        <v>economy</v>
       </c>
       <c r="B23" t="str">
-        <v>economy</v>
+        <v>/economy/</v>
       </c>
       <c r="C23" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D23" t="str">
         <v>经济</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24">
-        <v>23</v>
+      <c r="A24" t="str">
+        <v>ratio</v>
       </c>
       <c r="B24" t="str">
-        <v>ratio</v>
+        <v>/ratio/</v>
       </c>
       <c r="C24" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D24" t="str">
         <v>比率</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25">
-        <v>24</v>
+      <c r="A25" t="str">
+        <v>mean</v>
       </c>
       <c r="B25" t="str">
-        <v>mean</v>
+        <v>/miːn/</v>
       </c>
       <c r="C25" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D25" t="str">
         <v>意思</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26">
-        <v>25</v>
+      <c r="A26" t="str">
+        <v>dealer</v>
       </c>
       <c r="B26" t="str">
-        <v>dealer</v>
+        <v>/dealer/</v>
       </c>
       <c r="C26" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D26" t="str">
         <v>商人</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27">
-        <v>26</v>
+      <c r="A27" t="str">
+        <v>special</v>
       </c>
       <c r="B27" t="str">
-        <v>special</v>
+        <v>/special/</v>
       </c>
       <c r="C27" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D27" t="str">
         <v>特殊的</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28">
-        <v>27</v>
+      <c r="A28" t="str">
+        <v>edit</v>
       </c>
       <c r="B28" t="str">
-        <v>edit</v>
+        <v>/ˈedɪt/</v>
       </c>
       <c r="C28" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D28" t="str">
         <v>编辑</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29">
-        <v>28</v>
+      <c r="A29" t="str">
+        <v>thank</v>
       </c>
       <c r="B29" t="str">
-        <v>thank</v>
+        <v>/θæŋk/</v>
       </c>
       <c r="C29" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D29" t="str">
         <v>感谢</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30">
-        <v>29</v>
+      <c r="A30" t="str">
+        <v>rag</v>
       </c>
       <c r="B30" t="str">
-        <v>rag</v>
+        <v>/rag/</v>
       </c>
       <c r="C30" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D30" t="str">
         <v>破布</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31">
-        <v>30</v>
+      <c r="A31" t="str">
+        <v>curve</v>
       </c>
       <c r="B31" t="str">
-        <v>curve</v>
+        <v>/kɜːv/</v>
       </c>
       <c r="C31" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D31" t="str">
         <v>曲线</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32">
-        <v>31</v>
+      <c r="A32" t="str">
+        <v>heap</v>
       </c>
       <c r="B32" t="str">
-        <v>heap</v>
+        <v>/heap/</v>
       </c>
       <c r="C32" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D32" t="str">
         <v>堆</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33">
-        <v>32</v>
+      <c r="A33" t="str">
+        <v>interact</v>
       </c>
       <c r="B33" t="str">
-        <v>interact</v>
+        <v>/interact/</v>
       </c>
       <c r="C33" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D33" t="str">
         <v>互动</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34">
-        <v>33</v>
+      <c r="A34" t="str">
+        <v>reckless</v>
       </c>
       <c r="B34" t="str">
-        <v>reckless</v>
+        <v>/reckless/</v>
       </c>
       <c r="C34" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D34" t="str">
         <v>鲁莽的</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35">
-        <v>34</v>
+      <c r="A35" t="str">
+        <v>trace</v>
       </c>
       <c r="B35" t="str">
-        <v>trace</v>
+        <v>/treɪs/</v>
       </c>
       <c r="C35" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D35" t="str">
         <v>跟踪</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36">
-        <v>35</v>
+      <c r="A36" t="str">
+        <v>pause</v>
       </c>
       <c r="B36" t="str">
-        <v>pause</v>
+        <v>/pɔːz/</v>
       </c>
       <c r="C36" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D36" t="str">
         <v>暂停</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37">
-        <v>36</v>
+      <c r="A37" t="str">
+        <v>nylon</v>
       </c>
       <c r="B37" t="str">
-        <v>nylon</v>
+        <v>/nylon/</v>
       </c>
       <c r="C37" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D37" t="str">
         <v>尼龙</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38">
-        <v>37</v>
+      <c r="A38" t="str">
+        <v>responsible</v>
       </c>
       <c r="B38" t="str">
-        <v>responsible</v>
+        <v>/responsible/</v>
       </c>
       <c r="C38" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D38" t="str">
         <v>负责任的</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39">
-        <v>38</v>
+      <c r="A39" t="str">
+        <v>appliance</v>
       </c>
       <c r="B39" t="str">
-        <v>appliance</v>
+        <v>/appliance/</v>
       </c>
       <c r="C39" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D39" t="str">
         <v>器械</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40">
-        <v>39</v>
+      <c r="A40" t="str">
+        <v>bulb</v>
       </c>
       <c r="B40" t="str">
-        <v>bulb</v>
+        <v>/bulb/</v>
       </c>
       <c r="C40" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D40" t="str">
         <v>灯泡</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41">
-        <v>40</v>
+      <c r="A41" t="str">
+        <v>transmission</v>
       </c>
       <c r="B41" t="str">
-        <v>transmission</v>
+        <v>/transmission/</v>
       </c>
       <c r="C41" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D41" t="str">
         <v>传播</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42">
-        <v>41</v>
+      <c r="A42" t="str">
+        <v>pledge</v>
       </c>
       <c r="B42" t="str">
-        <v>pledge</v>
+        <v>/pledge/</v>
       </c>
       <c r="C42" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D42" t="str">
         <v>发誓</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43">
-        <v>42</v>
+      <c r="A43" t="str">
+        <v>mobile</v>
       </c>
       <c r="B43" t="str">
-        <v>mobile</v>
+        <v>/mobile/</v>
       </c>
       <c r="C43" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D43" t="str">
         <v>活动的</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44">
-        <v>43</v>
+      <c r="A44" t="str">
+        <v>sugar</v>
       </c>
       <c r="B44" t="str">
-        <v>sugar</v>
+        <v>/sugar/</v>
       </c>
       <c r="C44" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D44" t="str">
         <v>糖</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45">
-        <v>44</v>
+      <c r="A45" t="str">
+        <v>eye</v>
       </c>
       <c r="B45" t="str">
-        <v>eye</v>
+        <v>/eye/</v>
       </c>
       <c r="C45" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D45" t="str">
         <v>眼睛</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C45"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D45"/>
   </ignoredErrors>
 </worksheet>
 </file>